--- a/output/2026-08-31_13_Italia_Toscana_ATEX_Equipment_Services.xlsx
+++ b/output/2026-08-31_13_Italia_Toscana_ATEX_Equipment_Services.xlsx
@@ -494,10 +494,9 @@
           <t>0574 25801</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Azienda di Prato (Via Case Nuove 105) specializzata in impianti di aspirazione industriale, ventilatori per uso industriale e aspirazione di gas/fumo. Esistenza confermata su Europages e Virgilio Aziende oltre che sul sito ufficiale. Email generica non reperita nelle fonti consultate.</t>
+          <t>Azienda di Prato (Via Case Nuove 105) specializzata in impianti di aspirazione industriale, ventilatori per uso industriale e aspirazione di gas/fumo. Esistenza confermata su Europages e Virgilio Aziende oltre che sul sito ufficiale. Email generica non reperita nelle fonti consultate. [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -532,10 +531,9 @@
           <t>055 898001 / 055 898005 / 055 0941223</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Azienda attiva dal 2008 a Campi Bisenzio (FI), Via Fratelli Cervi 63, CF/P.IVA 05792470485, specializzata in impianti di aspirazione industriale, ventilatori industriali e sistemi antifumo. Confermata su Kompass, Europages e PagineGialle. Email generica non reperita.</t>
+          <t>Azienda attiva dal 2008 a Campi Bisenzio (FI), Via Fratelli Cervi 63, CF/P.IVA 05792470485, specializzata in impianti di aspirazione industriale, ventilatori industriali e sistemi antifumo. Confermata su Kompass, Europages e PagineGialle. Email generica non reperita. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -619,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Azienda storica (attiva dal 1979) di Montemurlo (PO), Via dell'Agricoltura 29-31-33, specializzata in impianti di aspirazione industriale, filtrazione aria e depurazione fumi. Confermata su misterimprese, PagineBianche e sito ufficiale.</t>
+          <t>Azienda storica (attiva dal 1979) di Montemurlo (PO), Via dell'Agricoltura 29-31-33, specializzata in impianti di aspirazione industriale, filtrazione aria e depurazione fumi. Confermata su misterimprese, PagineBianche e sito ufficiale. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -661,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sede in Via dei Fabbri 27/63, Uzzano (PT); attivita' di fabbricazione macchinari per aspirazione e filtrazione aria. Confermata su registri camerali (Kompass, Ufficio Camerale, Report Aziende) e sul sito ufficiale.</t>
+          <t>Sede in Via dei Fabbri 27/63, Uzzano (PT); attivita' di fabbricazione macchinari per aspirazione e filtrazione aria. Confermata su registri camerali (Kompass, Ufficio Camerale, Report Aziende) e sul sito ufficiale. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -696,7 +694,6 @@
           <t>0583 936856</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Azienda di Lunata, Capannori (LU), Via G. Pieraccini 11, attiva in saldatura/taglio/automazione, filtrazione e depurazione aria/fumi, gas tecnici. Fonti confermano disponibilita' di sistemi di aspirazione e bracci aspiranti in esecuzione antideflagrante per zone ATEX. ATTENZIONE: lo stesso indirizzo e lo stesso numero di telefono risultano condivisi con l'entita' collegata "Supra Cali Srl" (rete di distribuzione Air Liquide, P.IVA 01232790467). L'email indicata nella lista grezza (info@supracali.it) non e' stata attribuita con certezza a Supra Srl e viene lasciata vuota: va verificata manualmente per evitare confusione tra le due entita' collegate.</t>
@@ -783,7 +780,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Distributore dal 1988 di componenti elettrici/pneumatici/oleodinamici in Toscana, sede Via Gastone Razzaguta 24, Livorno. Confermata la distribuzione di elettrovalvole coassiali ATEX (zone 2G/2D) e la rappresentanza del brand Vortec.</t>
+          <t>Distributore dal 1988 di componenti elettrici/pneumatici/oleodinamici in Toscana, sede Via Gastone Razzaguta 24, Livorno. Confermata la distribuzione di elettrovalvole coassiali ATEX (zone 2G/2D) e la rappresentanza del brand Vortec. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -818,10 +815,9 @@
           <t>055 412804</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Azienda di Firenze (Via Orazio Vecchi 109) attiva dal 1998 nella vendita di macchine/attrezzature per pulizia industriale e civile. Le fonti confermano esplicitamente la vendita di aspiratori/aspiraliquidi professionali antideflagranti certificati ATEX. Email generica non reperita.</t>
+          <t>Azienda di Firenze (Via Orazio Vecchi 109) attiva dal 1998 nella vendita di macchine/attrezzature per pulizia industriale e civile. Le fonti confermano esplicitamente la vendita di aspiratori/aspiraliquidi professionali antideflagranti certificati ATEX. Email generica non reperita. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -935,11 +931,9 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sede reale in Localita' Pianacci, Bucine (AR) - non a Pisa come indicato nella lista grezza (indirizzo da correggere). P.IVA 01511090514. Confermata specializzazione in impianti di aspirazione con esecuzioni ATEX/antideflagranti, sistemi di rilevazione scintille e antincendio integrati, monitoraggio Industry 4.0. Telefono non riportato per discrepanza tra le fonti consultate (una fonte indica 055 9911297, un'altra 0559911015): da verificare manualmente. Email non reperita.</t>
+          <t>Sede reale in Localita' Pianacci, Bucine (AR) - non a Pisa come indicato nella lista grezza (indirizzo da correggere). P.IVA 01511090514. Confermata specializzazione in impianti di aspirazione con esecuzioni ATEX/antideflagranti, sistemi di rilevazione scintille e antincendio integrati, monitoraggio Industry 4.0. Telefono non riportato per discrepanza tra le fonti consultate (una fonte indica 055 9911297, un'altra 0559911015): da verificare manualmente. Email non reperita. [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -974,7 +968,6 @@
           <t>0572 427056</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Ragione sociale confermata "Tecnoimpianti Srl", P.IVA 01402160467, sede legale in Via delle Cartiere 217/B, Pescia (PT) - non genericamente "Lucca" come indicato nella lista grezza (indirizzo da correggere; operativita' anche in zona Lucca/Capannori). Specializzata in impianti di aspirazione polveri industriali per il settore cartario/tissue e sistemi di triturazione scarti/cabine insonorizzanti. Email generica non reperita.</t>
